--- a/artfynd/A 26791-2025 artfynd.xlsx
+++ b/artfynd/A 26791-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814940</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814966</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814952</v>
       </c>
       <c r="B4" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814977</v>
       </c>
       <c r="B6" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26791-2025 artfynd.xlsx
+++ b/artfynd/A 26791-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814940</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814966</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814952</v>
       </c>
       <c r="B4" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814977</v>
       </c>
       <c r="B6" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26791-2025 artfynd.xlsx
+++ b/artfynd/A 26791-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814940</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814966</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814952</v>
       </c>
       <c r="B4" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814951</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814977</v>
       </c>
       <c r="B6" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26791-2025 artfynd.xlsx
+++ b/artfynd/A 26791-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814940</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814966</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814952</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814951</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814977</v>
       </c>
       <c r="B6" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 26791-2025 artfynd.xlsx
+++ b/artfynd/A 26791-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814940</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814966</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814952</v>
       </c>
       <c r="B4" t="n">
-        <v>80142</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814951</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814977</v>
       </c>
       <c r="B6" t="n">
-        <v>78678</v>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
